--- a/inventory/files/2026-W40/STA_SA_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_SA_AUTO_2026-W40.xlsx
@@ -1539,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="14" min="1" max="1"/>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AH-MICRTOWEL12A1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/inventory/files/2026-W40/STA_SA_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_SA_AUTO_2026-W40.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
